--- a/docs/students/11b.xlsx
+++ b/docs/students/11b.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\María Alexandra\Listados Actualizados\LISTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\AgenteIA_Alexandra\docs\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB04D29-DD73-40AC-B571-D55204E20CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC3138C-069D-4595-B132-0679A452D8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,26 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t xml:space="preserve">CORREO MAMÁ </t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Correo institucional</t>
-  </si>
-  <si>
-    <t>Nombre mamá</t>
-  </si>
-  <si>
-    <t>Nombre papá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORREO PAPÁ </t>
-  </si>
-  <si>
     <t xml:space="preserve">Acosta Rozo Manuela </t>
   </si>
   <si>
@@ -147,24 +132,6 @@
     <t>jfhernandezm@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Marin Cuellar Naharesh Goel </t>
-  </si>
-  <si>
-    <t>Jimena Patricia Cuellar Marin</t>
-  </si>
-  <si>
-    <t>daemarin185@gmail.com</t>
-  </si>
-  <si>
-    <t>Juan Pablo Cuellar Marin</t>
-  </si>
-  <si>
-    <t>Juan.Pablo.Cuellar.Marin.79@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acudiente    daemarin185@gmail.com </t>
-  </si>
-  <si>
     <t xml:space="preserve">Mongui Ramirez Mariana </t>
   </si>
   <si>
@@ -300,9 +267,6 @@
     <t>23AC0330@cac.edu.co</t>
   </si>
   <si>
-    <t>23AC0343@cac.edu.co</t>
-  </si>
-  <si>
     <t>23AC0344@cac.edu.co</t>
   </si>
   <si>
@@ -325,13 +289,34 @@
   </si>
   <si>
     <t>23AC0336@cac.edu.co</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CORREO INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>NOMBRE MAMÁ</t>
+  </si>
+  <si>
+    <t>NOMBRE  PAPÁ</t>
+  </si>
+  <si>
+    <t>CORREO PAPÁ</t>
+  </si>
+  <si>
+    <t>ID_DRIVE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,12 +339,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Light"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -411,7 +390,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -422,9 +401,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -769,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="30.25" customWidth="1"/>
@@ -778,342 +755,363 @@
     <col min="4" max="4" width="31.25" customWidth="1"/>
     <col min="5" max="5" width="28.25" customWidth="1"/>
     <col min="6" max="6" width="39.875" customWidth="1"/>
-    <col min="7" max="7" width="36.125" customWidth="1"/>
+    <col min="7" max="7" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="72" customHeight="1">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" ht="15">
+    <row r="1" spans="1:7" ht="72" customHeight="1">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="G3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A17">
-    <sortCondition ref="A3:A17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A16">
+    <sortCondition ref="A3:A16"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
@@ -1126,30 +1124,30 @@
     <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
     <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
     <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
-    <hyperlink ref="F8" r:id="rId9" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
-    <hyperlink ref="F9" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
-    <hyperlink ref="D10" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
-    <hyperlink ref="F10" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
-    <hyperlink ref="D11" r:id="rId13" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
-    <hyperlink ref="D12" r:id="rId14" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
-    <hyperlink ref="D13" r:id="rId15" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
-    <hyperlink ref="F12" r:id="rId16" xr:uid="{00000000-0004-0000-0700-00000F000000}"/>
-    <hyperlink ref="F13" r:id="rId17" xr:uid="{00000000-0004-0000-0700-000010000000}"/>
-    <hyperlink ref="D14" r:id="rId18" xr:uid="{00000000-0004-0000-0700-000011000000}"/>
-    <hyperlink ref="F14" r:id="rId19" xr:uid="{00000000-0004-0000-0700-000012000000}"/>
-    <hyperlink ref="D15" r:id="rId20" xr:uid="{00000000-0004-0000-0700-000013000000}"/>
-    <hyperlink ref="F15" r:id="rId21" xr:uid="{00000000-0004-0000-0700-000014000000}"/>
-    <hyperlink ref="D16" r:id="rId22" xr:uid="{00000000-0004-0000-0700-000015000000}"/>
-    <hyperlink ref="F16" r:id="rId23" xr:uid="{00000000-0004-0000-0700-000016000000}"/>
-    <hyperlink ref="D17" r:id="rId24" xr:uid="{00000000-0004-0000-0700-000017000000}"/>
-    <hyperlink ref="F17" r:id="rId25" xr:uid="{00000000-0004-0000-0700-000018000000}"/>
-    <hyperlink ref="G9" r:id="rId26" display="daemarin185@gmail.com " xr:uid="{00000000-0004-0000-0700-000019000000}"/>
-    <hyperlink ref="D3" r:id="rId27" xr:uid="{00000000-0004-0000-0700-00001A000000}"/>
-    <hyperlink ref="D5" r:id="rId28" xr:uid="{00000000-0004-0000-0700-00001B000000}"/>
-    <hyperlink ref="F5" r:id="rId29" xr:uid="{00000000-0004-0000-0700-00001C000000}"/>
-    <hyperlink ref="B5" r:id="rId30" display="23AC0327@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0700-00001D000000}"/>
-    <hyperlink ref="F3" r:id="rId31" xr:uid="{00000000-0004-0000-0700-00001E000000}"/>
+    <hyperlink ref="F8" r:id="rId8" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="D9" r:id="rId9" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
+    <hyperlink ref="F9" r:id="rId10" xr:uid="{00000000-0004-0000-0700-00000B000000}"/>
+    <hyperlink ref="D10" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000C000000}"/>
+    <hyperlink ref="D11" r:id="rId12" xr:uid="{00000000-0004-0000-0700-00000D000000}"/>
+    <hyperlink ref="D12" r:id="rId13" xr:uid="{00000000-0004-0000-0700-00000E000000}"/>
+    <hyperlink ref="F11" r:id="rId14" xr:uid="{00000000-0004-0000-0700-00000F000000}"/>
+    <hyperlink ref="F12" r:id="rId15" xr:uid="{00000000-0004-0000-0700-000010000000}"/>
+    <hyperlink ref="D13" r:id="rId16" xr:uid="{00000000-0004-0000-0700-000011000000}"/>
+    <hyperlink ref="F13" r:id="rId17" xr:uid="{00000000-0004-0000-0700-000012000000}"/>
+    <hyperlink ref="D14" r:id="rId18" xr:uid="{00000000-0004-0000-0700-000013000000}"/>
+    <hyperlink ref="F14" r:id="rId19" xr:uid="{00000000-0004-0000-0700-000014000000}"/>
+    <hyperlink ref="D15" r:id="rId20" xr:uid="{00000000-0004-0000-0700-000015000000}"/>
+    <hyperlink ref="F15" r:id="rId21" xr:uid="{00000000-0004-0000-0700-000016000000}"/>
+    <hyperlink ref="D16" r:id="rId22" xr:uid="{00000000-0004-0000-0700-000017000000}"/>
+    <hyperlink ref="F16" r:id="rId23" xr:uid="{00000000-0004-0000-0700-000018000000}"/>
+    <hyperlink ref="D3" r:id="rId24" xr:uid="{00000000-0004-0000-0700-00001A000000}"/>
+    <hyperlink ref="D5" r:id="rId25" xr:uid="{00000000-0004-0000-0700-00001B000000}"/>
+    <hyperlink ref="F5" r:id="rId26" xr:uid="{00000000-0004-0000-0700-00001C000000}"/>
+    <hyperlink ref="B5" r:id="rId27" display="23AC0327@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0700-00001D000000}"/>
+    <hyperlink ref="F3" r:id="rId28" xr:uid="{00000000-0004-0000-0700-00001E000000}"/>
+    <hyperlink ref="G3" r:id="rId29" xr:uid="{1FB1BAE3-0623-4BF7-A535-CA61CB3ED64B}"/>
+    <hyperlink ref="G4:G13" r:id="rId30" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{99B5077E-BEAB-497B-85DD-8A3393168A88}"/>
+    <hyperlink ref="G14:G16" r:id="rId31" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{E61FCBEF-28F2-4D22-96D5-86BC89FCB9C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1294,18 +1292,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1327,18 +1325,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBBEA71-C632-4AE8-B7C8-3F289DADFCB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35073413-9516-4B73-8842-99BBF230AC45}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBBEA71-C632-4AE8-B7C8-3F289DADFCB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>